--- a/assets/OJT-Template-Bulk-Logging.xlsx
+++ b/assets/OJT-Template-Bulk-Logging.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gian\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gian\Documents\OJTTracking\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74AFD8AC-74CA-491B-ACF6-17056F1853BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BC969D-58B5-4458-8921-240A1F04EA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{2AB8DEA5-93CD-4CFD-B462-D8363C9FF3D0}"/>
   </bookViews>
@@ -71,16 +71,6 @@
     <t>!!! INSTRUCTIONS !!!</t>
   </si>
   <si>
-    <t>-Do not change column names
--Date format: YYYY-MM-DD
--Time format: 24-hour (HH:MM)
--Break (mins): lunch/break duration in minutes
--Hours auto-calculates using Time In/Out minus Break
--If Hours is blank, it will be computed automatically
--You may still override Hours manually if needed
--Avoid duplicate dates unless intentional</t>
-  </si>
-  <si>
     <t>Present</t>
   </si>
   <si>
@@ -101,14 +91,25 @@
   <si>
     <t>System Development</t>
   </si>
+  <si>
+    <t>-Do not change column names
+-Date format: YYYY-MM-DD
+-Time format: 24-hour (HH:MM)
+-Break (mins): lunch/break duration in minutes
+-Hours auto-calculates using Time In/Out minus Break
+-If Hours is blank, it will be computed automatically
+-You may still override Hours manually if needed
+-Avoid duplicate dates unless intentional
+-Don't add empty row between records</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="173" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm\ AM/PM;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -165,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -215,15 +216,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -234,82 +226,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -320,95 +241,71 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -747,27 +644,27 @@
   <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="17" customWidth="1"/>
-    <col min="2" max="3" width="20.7109375" style="20" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" style="33" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="6" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" style="9" customWidth="1"/>
+    <col min="4" max="5" width="20.7109375" style="16" customWidth="1"/>
     <col min="6" max="7" width="20.7109375" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -776,451 +673,499 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="26"/>
-      <c r="I3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="8"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="19"/>
+      <c r="I3" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="27">
+      <c r="A4" s="10">
         <v>46118</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="27">
+      <c r="A5" s="10">
         <v>46119</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="11">
         <v>0.32430555555555557</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="11">
         <v>0.73055555555555551</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="15">
         <v>60</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="15">
         <f>((C5-B5)*24) - (D5/60)</f>
         <v>8.7499999999999982</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="11"/>
+      <c r="F5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
+      <c r="A6" s="10">
         <v>46120</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="11">
         <v>0.3347222222222222</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="11">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D6" s="32">
-        <v>0</v>
-      </c>
-      <c r="E6" s="32">
+      <c r="D6" s="15">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15">
         <f t="shared" ref="E6:E7" si="0">((C6-B6)*24) - (D6/60)</f>
         <v>4.4666666666666686</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="11"/>
+      <c r="F6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
+      <c r="A7" s="10">
         <v>46121</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="11">
         <v>0.50069444444444444</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="11">
         <v>0.75277777777777777</v>
       </c>
-      <c r="D7" s="32">
-        <v>0</v>
-      </c>
-      <c r="E7" s="32">
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
         <f t="shared" si="0"/>
         <v>6.05</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="11"/>
+      <c r="F7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="11"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="11"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31">
+      <c r="A10" s="5"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14">
         <f>((C10-B10)*24) - (D10/60)</f>
         <v>0</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="11"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31">
+      <c r="A11" s="5"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14">
         <f t="shared" ref="E11:E74" si="1">((C11-B11)*24) - (D11/60)</f>
         <v>0</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="11"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31">
+      <c r="A12" s="5"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="11"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31">
+      <c r="A13" s="5"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="14"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31">
+      <c r="A14" s="5"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31">
+      <c r="A15" s="5"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31">
+      <c r="A16" s="5"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31">
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="16"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31">
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31">
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31">
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31">
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31">
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31">
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31">
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31">
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31">
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1228,11 +1173,11 @@
       <c r="G32" s="2"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31">
+      <c r="A33" s="5"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1240,11 +1185,11 @@
       <c r="G33" s="2"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31">
+      <c r="A34" s="5"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1252,11 +1197,11 @@
       <c r="G34" s="2"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31">
+      <c r="A35" s="5"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1264,11 +1209,11 @@
       <c r="G35" s="2"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31">
+      <c r="A36" s="5"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1276,11 +1221,11 @@
       <c r="G36" s="2"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31">
+      <c r="A37" s="5"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1288,11 +1233,11 @@
       <c r="G37" s="2"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31">
+      <c r="A38" s="5"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1300,11 +1245,11 @@
       <c r="G38" s="2"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="16"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31">
+      <c r="A39" s="5"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1312,11 +1257,11 @@
       <c r="G39" s="2"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31">
+      <c r="A40" s="5"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1324,11 +1269,11 @@
       <c r="G40" s="2"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31">
+      <c r="A41" s="5"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1336,11 +1281,11 @@
       <c r="G41" s="2"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31">
+      <c r="A42" s="5"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1348,11 +1293,11 @@
       <c r="G42" s="2"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31">
+      <c r="A43" s="5"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1360,11 +1305,11 @@
       <c r="G43" s="2"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="16"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31">
+      <c r="A44" s="5"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1372,11 +1317,11 @@
       <c r="G44" s="2"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31">
+      <c r="A45" s="5"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1384,11 +1329,11 @@
       <c r="G45" s="2"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="16"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31">
+      <c r="A46" s="5"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1396,11 +1341,11 @@
       <c r="G46" s="2"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="16"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31">
+      <c r="A47" s="5"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1408,11 +1353,11 @@
       <c r="G47" s="2"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="16"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31">
+      <c r="A48" s="5"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1420,11 +1365,11 @@
       <c r="G48" s="2"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31">
+      <c r="A49" s="5"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1432,11 +1377,11 @@
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="16"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31">
+      <c r="A50" s="5"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1444,11 +1389,11 @@
       <c r="G50" s="2"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31">
+      <c r="A51" s="5"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1456,11 +1401,11 @@
       <c r="G51" s="2"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="16"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31">
+      <c r="A52" s="5"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1468,11 +1413,11 @@
       <c r="G52" s="2"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="16"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31">
+      <c r="A53" s="5"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1480,11 +1425,11 @@
       <c r="G53" s="2"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="16"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31">
+      <c r="A54" s="5"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1492,11 +1437,11 @@
       <c r="G54" s="2"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="16"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31">
+      <c r="A55" s="5"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1504,11 +1449,11 @@
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="16"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31">
+      <c r="A56" s="5"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1516,11 +1461,11 @@
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="16"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31">
+      <c r="A57" s="5"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1528,11 +1473,11 @@
       <c r="G57" s="2"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="16"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31">
+      <c r="A58" s="5"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1540,11 +1485,11 @@
       <c r="G58" s="2"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="16"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31">
+      <c r="A59" s="5"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1552,11 +1497,11 @@
       <c r="G59" s="2"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="16"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31">
+      <c r="A60" s="5"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1564,11 +1509,11 @@
       <c r="G60" s="2"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="16"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31">
+      <c r="A61" s="5"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1576,11 +1521,11 @@
       <c r="G61" s="2"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="16"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31">
+      <c r="A62" s="5"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1588,11 +1533,11 @@
       <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="16"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31">
+      <c r="A63" s="5"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1600,11 +1545,11 @@
       <c r="G63" s="2"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="16"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31">
+      <c r="A64" s="5"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1612,11 +1557,11 @@
       <c r="G64" s="2"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="16"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31">
+      <c r="A65" s="5"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1624,11 +1569,11 @@
       <c r="G65" s="2"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="16"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31">
+      <c r="A66" s="5"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1636,11 +1581,11 @@
       <c r="G66" s="2"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="16"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31">
+      <c r="A67" s="5"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1648,11 +1593,11 @@
       <c r="G67" s="2"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="16"/>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="31"/>
-      <c r="E68" s="31">
+      <c r="A68" s="5"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1660,11 +1605,11 @@
       <c r="G68" s="2"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="16"/>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31">
+      <c r="A69" s="5"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1672,11 +1617,11 @@
       <c r="G69" s="2"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="16"/>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31">
+      <c r="A70" s="5"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1684,11 +1629,11 @@
       <c r="G70" s="2"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="16"/>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="31">
+      <c r="A71" s="5"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1696,11 +1641,11 @@
       <c r="G71" s="2"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="16"/>
-      <c r="B72" s="19"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31">
+      <c r="A72" s="5"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1708,11 +1653,11 @@
       <c r="G72" s="2"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="16"/>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="31">
+      <c r="A73" s="5"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1720,11 +1665,11 @@
       <c r="G73" s="2"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="16"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="31"/>
-      <c r="E74" s="31">
+      <c r="A74" s="5"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1732,11 +1677,11 @@
       <c r="G74" s="2"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="16"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31">
+      <c r="A75" s="5"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14">
         <f t="shared" ref="E75:E100" si="2">((C75-B75)*24) - (D75/60)</f>
         <v>0</v>
       </c>
@@ -1744,11 +1689,11 @@
       <c r="G75" s="2"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="16"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="31"/>
-      <c r="E76" s="31">
+      <c r="A76" s="5"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1756,11 +1701,11 @@
       <c r="G76" s="2"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="16"/>
-      <c r="B77" s="19"/>
-      <c r="C77" s="19"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="31">
+      <c r="A77" s="5"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1768,11 +1713,11 @@
       <c r="G77" s="2"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="16"/>
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="31">
+      <c r="A78" s="5"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1780,11 +1725,11 @@
       <c r="G78" s="2"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="16"/>
-      <c r="B79" s="19"/>
-      <c r="C79" s="19"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31">
+      <c r="A79" s="5"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1792,11 +1737,11 @@
       <c r="G79" s="2"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="16"/>
-      <c r="B80" s="19"/>
-      <c r="C80" s="19"/>
-      <c r="D80" s="31"/>
-      <c r="E80" s="31">
+      <c r="A80" s="5"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1804,11 +1749,11 @@
       <c r="G80" s="2"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="16"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
-      <c r="D81" s="31"/>
-      <c r="E81" s="31">
+      <c r="A81" s="5"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1816,11 +1761,11 @@
       <c r="G81" s="2"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="16"/>
-      <c r="B82" s="19"/>
-      <c r="C82" s="19"/>
-      <c r="D82" s="31"/>
-      <c r="E82" s="31">
+      <c r="A82" s="5"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1828,11 +1773,11 @@
       <c r="G82" s="2"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="16"/>
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
-      <c r="D83" s="31"/>
-      <c r="E83" s="31">
+      <c r="A83" s="5"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1840,11 +1785,11 @@
       <c r="G83" s="2"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="16"/>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="31"/>
-      <c r="E84" s="31">
+      <c r="A84" s="5"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1852,11 +1797,11 @@
       <c r="G84" s="2"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="16"/>
-      <c r="B85" s="19"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="31"/>
-      <c r="E85" s="31">
+      <c r="A85" s="5"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1864,11 +1809,11 @@
       <c r="G85" s="2"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="16"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="31">
+      <c r="A86" s="5"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1876,11 +1821,11 @@
       <c r="G86" s="2"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="16"/>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31">
+      <c r="A87" s="5"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1888,11 +1833,11 @@
       <c r="G87" s="2"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="16"/>
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-      <c r="D88" s="31"/>
-      <c r="E88" s="31">
+      <c r="A88" s="5"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1900,11 +1845,11 @@
       <c r="G88" s="2"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="16"/>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="31"/>
-      <c r="E89" s="31">
+      <c r="A89" s="5"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1912,11 +1857,11 @@
       <c r="G89" s="2"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="16"/>
-      <c r="B90" s="19"/>
-      <c r="C90" s="19"/>
-      <c r="D90" s="31"/>
-      <c r="E90" s="31">
+      <c r="A90" s="5"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1924,11 +1869,11 @@
       <c r="G90" s="2"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="16"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="31"/>
-      <c r="E91" s="31">
+      <c r="A91" s="5"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1936,11 +1881,11 @@
       <c r="G91" s="2"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="16"/>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="31"/>
-      <c r="E92" s="31">
+      <c r="A92" s="5"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1948,11 +1893,11 @@
       <c r="G92" s="2"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="16"/>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="31"/>
-      <c r="E93" s="31">
+      <c r="A93" s="5"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1960,11 +1905,11 @@
       <c r="G93" s="2"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="16"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="19"/>
-      <c r="D94" s="31"/>
-      <c r="E94" s="31">
+      <c r="A94" s="5"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1972,11 +1917,11 @@
       <c r="G94" s="2"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="16"/>
-      <c r="B95" s="19"/>
-      <c r="C95" s="19"/>
-      <c r="D95" s="31"/>
-      <c r="E95" s="31">
+      <c r="A95" s="5"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1984,11 +1929,11 @@
       <c r="G95" s="2"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="16"/>
-      <c r="B96" s="19"/>
-      <c r="C96" s="19"/>
-      <c r="D96" s="31"/>
-      <c r="E96" s="31">
+      <c r="A96" s="5"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1996,11 +1941,11 @@
       <c r="G96" s="2"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="16"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="31"/>
-      <c r="E97" s="31">
+      <c r="A97" s="5"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2008,11 +1953,11 @@
       <c r="G97" s="2"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="16"/>
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-      <c r="D98" s="31"/>
-      <c r="E98" s="31">
+      <c r="A98" s="5"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2020,11 +1965,11 @@
       <c r="G98" s="2"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="16"/>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="31"/>
-      <c r="E99" s="31">
+      <c r="A99" s="5"/>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2032,11 +1977,11 @@
       <c r="G99" s="2"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="16"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31">
+      <c r="A100" s="5"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2048,7 +1993,7 @@
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="I1:L2"/>
-    <mergeCell ref="I3:L13"/>
+    <mergeCell ref="I3:L25"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{9ED55B8F-8A39-45AD-B480-7C0A496E52B4}">
